--- a/assets/pdf/Resultados Meeting Fernando Alves.xlsx
+++ b/assets/pdf/Resultados Meeting Fernando Alves.xlsx
@@ -5,10 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Folha1" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Resultados" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Recordes" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
